--- a/simple_simulation/sheath_potential_comparison.xlsx
+++ b/simple_simulation/sheath_potential_comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\semi\Plasma_simulation\plasma_etch_simulation\simple_simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDD32B4-9520-4CF4-A7D4-F69C595CA0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBACC4E-1539-434F-8278-2C877FD92C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="1580" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,6 +96,3240 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>T=2.5eV</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y_t (U 2.5eV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5E8C-427B-A5D1-4742E40453E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y_p (Sim 2.5eV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>6.7019122059316816</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.767844982168401</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.586264526945679</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1920293709350198</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4417974796655879</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.060645614318575</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.88255339006542644</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.81146898391548428</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.75131275409500264</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.615415357576235</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71345966901923941</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5E8C-427B-A5D1-4742E40453E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="899674735"/>
+        <c:axId val="895362959"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="899674735"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="895362959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="895362959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="899674735"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>T=5eV</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y_t (U 5eV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9070-4A8D-AD38-566829529F00}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$2:$H$12</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9070-4A8D-AD38-566829529F00}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y_p (Sim 5.0eV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>12.635117928249789</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.1168093380592</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.6758160303513723</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5360767660630832</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.774989857770793</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.4093390620474211</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.27428987335757</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0623437515676379</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.053495539168614</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.007344756859391</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.99032893183974369</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9070-4A8D-AD38-566829529F00}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="938359055"/>
+        <c:axId val="895415759"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="938359055"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="895415759"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="895415759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="938359055"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>T=10 eV</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y_t (U 10eV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$2:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DFD2-4024-88E7-AFFCF7DE0F71}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y_p (Sim 10.0eV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$L$2:$L$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>21.424313847951659</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.08339137611857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9541483551498837</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9297894357300298</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.3491826693442999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.921497865816294</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7444773283896859</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.843386191072059</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.572959958117832</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5067926412550581</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.3635139346142919</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DFD2-4024-88E7-AFFCF7DE0F71}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="930505727"/>
+        <c:axId val="895373519"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="930505727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="895373519"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="895373519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="930505727"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>425543</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>102052</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>215446</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5F77774-1A07-A855-00F9-B86563488DD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>375122</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>184216</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>28863</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>101022</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59274FFA-0BAA-F367-D077-F269761637B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>173840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>375227</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>57726</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC72B7DD-B706-4827-4E5E-75B79E6F02A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -705,5 +3939,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>